--- a/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
+++ b/ModeOfDelivery/BCIO-mode_of_delivery-hierarchy.xlsx
@@ -443,32 +443,32 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>subontology</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>informaldefinition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>examples</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>informaldefinition</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>subontology</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>crossreference</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>examples</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OBI:0000011</t>
+          <t>BFO:0000144</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -587,7 +587,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>planned process</t>
+          <t>process profile</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
@@ -598,14 +598,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>A process that realizes a plan which is the concretization of a plan specification.</t>
+          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BCIO:037000</t>
+          <t>BCIO:043000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -614,7 +614,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>intervention</t>
+          <t>process attribute</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -624,14 +624,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>A planned process that has the aim of influencing an outcome.</t>
+          <t>A process profile that is an attribute of a process.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BCIO:003000</t>
+          <t>BCIO:050315</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -641,7 +641,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>behaviour change intervention</t>
+          <t>BCI attribute</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -650,14 +650,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>An intervention that has the aim of influencing human behaviour.</t>
+          <t>A process attribute whose bearer is a behaviour change intervention.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BCIO:050557</t>
+          <t>BCIO:011000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -668,7 +668,7 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>social influence intervention through mass media</t>
+          <t>behaviour change intervention mode of delivery</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -676,74 +676,94 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>A behaviour change intervention that is an awareness of other people’s thoughts, feelings and actions BCT delivered through a mass media mode of delivery.</t>
+          <t>An attribute of a BCI delivery that is the physical or informational medium through which a BCI is provided.</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr"/>
+          <t>For relevant subclasses, check &lt;process mode of delivery&gt;.</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>BCI mode of delivery</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BFO:0000144</t>
+          <t>BCIO:050996</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>process profile</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>process mode of delivery</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>b is a process_profile =Def. there is some process c such that b process_profile_of c (axiom label in BFO2 Reference: [093-002])</t>
-        </is>
-      </c>
+          <t>An attribute of a process that is the physical or informational medium through which a process is provided.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BCIO:043000</t>
+          <t>BCIO:011061</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>process attribute</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>asynchronous mode of delivery</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>A process profile that is an attribute of a process.</t>
-        </is>
-      </c>
+          <t>Mode of delivery that involves receipt of the intervention or its components taking place a significant period of time after delivery.</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BCIO:050315</t>
+          <t>BCIO:011058</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -751,25 +771,33 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>BCI attribute</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>uni-directional mode of delivery</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>A process attribute whose bearer is a behaviour change intervention.</t>
-        </is>
-      </c>
+          <t>Mode of delivery in which the only causal influence is from the intervention source to the recipient.</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BCIO:011000</t>
+          <t>BCIO:011034</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -780,7 +808,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>behaviour change intervention mode of delivery</t>
+          <t>somatic mode of delivery</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -788,31 +816,22 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>An attribute of a BCI delivery that is the physical or informational medium through which a BCI is provided.</t>
+          <t>Mode of delivery that involves devices or substances that alter bodily processes or structure.</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>For relevant subclasses, check &lt;process mode of delivery&gt;.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>BCI mode of delivery</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
+          <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BCIO:050996</t>
+          <t>BCIO:011035</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -820,18 +839,23 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>process mode of delivery</t>
-        </is>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ingestion mode of delivery</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>An attribute of a process that is the physical or informational medium through which a process is provided.</t>
+          <t>Somatic mode of delivery that involves ingestion of a chemical into the body.</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -841,7 +865,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BCIO:011063</t>
+          <t>BCIO:011036</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -850,32 +874,32 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>pull mode of delivery</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>transdermal mode of delivery</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Mode of delivery that requires some action on the part of the recipient.</t>
+          <t>Ingestion mode of delivery that involves ingestion of a chemical through the skin.</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BCIO:011056</t>
+          <t>BCIO:011041</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -884,32 +908,32 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>pair-based mode of delivery</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>inhalation mode of delivery</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves two recipients in the location where the intervention is delivered who have an interpersonal relationship.</t>
+          <t>Ingestion mode of delivery that involves absorption of a chemical through  the upper airways or lungs by inspiration.</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BCIO:011054</t>
+          <t>BCIO:011037</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -918,37 +942,32 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>somatic alteration mode of delivery</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>alimentary mode of delivery</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Mode of of delivery that involves modifying the structure of the body of the recipient of the intervention.</t>
+          <t>Somatic mode of delivery that involves ingestion of a chemical through the stomach or intestine.</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Includes surgery.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BCIO:011060</t>
+          <t>BCIO:011039</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -957,32 +976,32 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>synchronous mode of delivery</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ingestable liquid mode of delivery</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves delivery and receipt of the intervention or its components occurring at the same time or very close in time.</t>
+          <t>Alimentary mode of delivery that involves swallowing of a liquid.</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BCIO:011061</t>
+          <t>BCIO:011038</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -991,32 +1010,32 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>asynchronous mode of delivery</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>pill mode of delivery</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves receipt of the intervention or its components taking place a significant period of time after delivery.</t>
+          <t>Alimentary mode of delivery that involves swallowing of a pill or oral capsule.</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BCIO:011034</t>
+          <t>BCIO:011040</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1025,32 +1044,32 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>somatic mode of delivery</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>buccal mode of delivery</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves devices or substances that alter bodily processes or structure.</t>
+          <t>Ingestion mode of delivery that involves absorption of a chemical through the lining of the buccal cavity.</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BCIO:011047</t>
+          <t>BCIO:011042</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1060,36 +1079,31 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>chewable substance mode of delivery</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>injection mode of delivery</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves chewing of a soft material.</t>
+          <t>Ingestion mode of delivery that involves a chemical being introduced into body tissue through a hollow needle that punctures the skin.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>This includes chewing gum. often involves ingestion of a chemical that is released by chewing and absorbed through the lining of the buccal cavity, but this is not necessary.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BCIO:011048</t>
+          <t>BCIO:011045</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1099,31 +1113,31 @@
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>physical stimulus mode of delivery</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>intramuscular injection mode of delivery</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>A mode of delivery that involves application of a physical stimulus to the body.</t>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is muscle.</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BCIO:011050</t>
+          <t>BCIO:011044</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1134,30 +1148,30 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>temperature mode of delivery</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>intravenous injection mode of delivery</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Physical stimulius mode of delivery that involves application of heat or cold to the body.</t>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is venous blood.</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BCIO:011049</t>
+          <t>BCIO:011043</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1168,34 +1182,30 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>light exposure mode of delivery</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>subcutaneous injection mode of delivery</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves exposure of light to the body</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Includes photo therapy</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
+          <t>Injection mode of delivery in which the tissue receiving the chemical is subcutaneous tissue.</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BCIO:011051</t>
+          <t>BCIO:011046</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1208,19 +1218,24 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>electrical stimulation mode of delivery</t>
+          <t>wearable ingestion mode of delivery</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves application of electrical stimulation to the body.</t>
+          <t>Ingestion mode of delivery that involves a device that is worn on the body.</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes insulin pump.</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
@@ -1229,7 +1244,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BCIO:011052</t>
+          <t>BCIO:011048</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1239,36 +1254,31 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>physical pressure mode of delivery</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>physical stimulus mode of delivery</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves application of physical pressure to the outside of the body.</t>
+          <t>A mode of delivery that involves application of a physical stimulus to the body.</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Includes massage.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BCIO:011053</t>
+          <t>BCIO:011049</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1281,28 +1291,32 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>wearable stimulus mode of delivery</t>
+          <t>light exposure mode of delivery</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Physical stimulus mode of delivery that involves a device that is worn on the body.</t>
+          <t>Physical stimulus mode of delivery that involves exposure of light to the body</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Includes photo therapy</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BCIO:011035</t>
+          <t>BCIO:011053</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1312,31 +1326,31 @@
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>ingestion mode of delivery</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>wearable stimulus mode of delivery</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Somatic mode of delivery that involves ingestion of a chemical into the body.</t>
+          <t>Physical stimulus mode of delivery that involves a device that is worn on the body.</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BCIO:011042</t>
+          <t>BCIO:011050</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -1349,28 +1363,28 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>injection mode of delivery</t>
+          <t>temperature mode of delivery</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves a chemical being introduced into body tissue through a hollow needle that punctures the skin.</t>
+          <t>Physical stimulius mode of delivery that involves application of heat or cold to the body.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BCIO:011043</t>
+          <t>BCIO:011051</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -1381,30 +1395,30 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>subcutaneous injection mode of delivery</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>electrical stimulation mode of delivery</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is subcutaneous tissue.</t>
+          <t>Physical stimulus mode of delivery that involves application of electrical stimulation to the body.</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BCIO:011044</t>
+          <t>BCIO:011052</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1415,21 +1429,26 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>intravenous injection mode of delivery</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>physical pressure mode of delivery</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is venous blood.</t>
+          <t>Physical stimulus mode of delivery that involves application of physical pressure to the outside of the body.</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes massage.</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr"/>
@@ -1438,7 +1457,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BCIO:011045</t>
+          <t>BCIO:011047</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1448,22 +1467,27 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>chewable substance mode of delivery</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>intramuscular injection mode of delivery</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Injection mode of delivery in which the tissue receiving the chemical is muscle.</t>
+          <t>Ingestion mode of delivery that involves chewing of a soft material.</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>This includes chewing gum. often involves ingestion of a chemical that is released by chewing and absorbed through the lining of the buccal cavity, but this is not necessary.</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr"/>
@@ -1472,7 +1496,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>BCIO:011037</t>
+          <t>BCIO:011001</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1481,23 +1505,28 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>informational mode of delivery</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>alimentary mode of delivery</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Somatic mode of delivery that involves ingestion of a chemical through the stomach or intestine.</t>
+          <t>Mode of delivery that involves intentional transmission of a representation of the world to an intervention recipient with the aim of changing that person's representation of the world.</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>This includes delivery of rewards, prompts, and cues that result in learning and information about the environment and environmental contingencies.</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr"/>
@@ -1506,7 +1535,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BCIO:011038</t>
+          <t>BCIO:011010</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -1516,31 +1545,31 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>electronic mode of delivery</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>pill mode of delivery</t>
-        </is>
-      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Alimentary mode of delivery that involves swallowing of a pill or oral capsule.</t>
+          <t>Informational mode of delivery that involves electronic technology in the presentation of information to an intervention recipient.</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BCIO:011039</t>
+          <t>BCIO:011011</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1551,21 +1580,26 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>ingestable liquid mode of delivery</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>television mode of delivery</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Alimentary mode of delivery that involves swallowing of a liquid.</t>
+          <t>Electronic mode of delivery that involves presentation of information that is broadcast and displayed by television.</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes internet and satellite television.</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr"/>
@@ -1574,7 +1608,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BCIO:011040</t>
+          <t>BCIO:011017</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1587,19 +1621,24 @@
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>buccal mode of delivery</t>
+          <t>3-D projection mode of delivery</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves absorption of a chemical through the lining of the buccal cavity.</t>
+          <t>Electronic mode of delivery that involves presentation of a 3-D image.</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes hologram but does not include virtual reality headsets.</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr"/>
@@ -1608,7 +1647,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>BCIO:011036</t>
+          <t>BCIO:011019</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -1621,19 +1660,24 @@
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>transdermal mode of delivery</t>
+          <t>playable electronic storage mode of delivery</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves ingestion of a chemical through the skin.</t>
+          <t>Electronic mode of delivery that involves presentation of information stored on an object that is inserted into a playing device.</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes cassettes, video tapes, DVDs, CDs.</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr"/>
@@ -1642,7 +1686,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BCIO:011046</t>
+          <t>BCIO:011016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -1655,24 +1699,24 @@
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>wearable ingestion mode of delivery</t>
+          <t>electronic environmental object mode of delivery</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves a device that is worn on the body.</t>
+          <t>Electronic mode of delivery that involves an electronic device positioned in the environment of the intervention recipient that can gather information and respond to commands.</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Includes insulin pump.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes robots, and 'internet of things'.</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr"/>
@@ -1681,7 +1725,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BCIO:011041</t>
+          <t>BCIO:011029</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -1694,28 +1738,28 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>inhalation mode of delivery</t>
+          <t>e-book mode of delivery</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Ingestion mode of delivery that involves absorption of a chemical through  the upper airways or lungs by inspiration.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient being given access to an e-book.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BCIO:011001</t>
+          <t>BCIO:011026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -1724,37 +1768,32 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>informational mode of delivery</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>video game mode of delivery</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves intentional transmission of a representation of the world to an intervention recipient with the aim of changing that person's representation of the world.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient playing a computer game.</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>This includes delivery of rewards, prompts, and cues that result in learning and information about the environment and environmental contingencies.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BCIO:050556</t>
+          <t>BCIO:050558</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1764,36 +1803,31 @@
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>mass media mode of delivery</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>online press mode of delivery</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Informational mode of delivery of radio broadcast, television, online press and printed press to a mass audience.</t>
+          <t>Electronic mode of delivery of a newspaper or magazine.</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>This is a form of mass media.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BCIO:011031</t>
+          <t>BCIO:011020</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1803,22 +1837,27 @@
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>visual informational mode of delivery</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>radio broadcast mode of delivery</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves visual images.</t>
+          <t>Electronic mode of delivery that involves presentation of audio information that is broadcast and received by a radio receiver.</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes digital radio and audio that is streamed as a podcast.</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr"/>
@@ -1827,7 +1866,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BCIO:011030</t>
+          <t>BCIO:011014</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1837,31 +1876,31 @@
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>audio informational mode of delivery</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>electronic billboard mode of delivery</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves sound.</t>
+          <t>Electronic mode of delivery that involves presentation of information by an electronic screen positioned in a public location.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BCIO:011002</t>
+          <t>BCIO:011013</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1871,31 +1910,31 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>human interactional mode of delivery</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>computer mode of delivery</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves a person as intervention source who interacts with an intervention recipient in real time.</t>
+          <t>Electronic mode of delivery that involves presentation of information by a desktop or laptop computer.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BCIO:011004</t>
+          <t>BCIO:011027</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1908,28 +1947,28 @@
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>at-a-distance mode of delivery</t>
+          <t>website mode of delivery</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Human interactional mode of delivery that involves an intervention source and recipient being in different locations and communicating through a communication channel.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient interacting with a website.</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BCIO:011003</t>
+          <t>BCIO:011012</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1942,28 +1981,28 @@
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>face to face mode of delivery</t>
+          <t>mobile digital device mode of delivery</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Human interactional mode of delivery that involves an intervention source and recipient being together in the same location and communicating directly.</t>
+          <t>Electronic mode of delivery that involves presentation of information by a handheld mobile digital device that can store, retrieve and process data.</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BCIO:011005</t>
+          <t>BCIO:011018</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1973,36 +2012,31 @@
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>printed material mode of delivery</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>virtual reality mode of delivery</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves use of printed material.</t>
+          <t>Electronic mode of delivery that involves use of virtual reality through a virtual reality headset and optionally body movement sensors.</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Can include paper, acetate, text, diagrams and photographic images.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q47" t="inlineStr"/>
       <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BCIO:011006</t>
+          <t>BCIO:011015</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2015,19 +2049,24 @@
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>letter mode of delivery</t>
+          <t>wearable electronic device mode of delivery</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves a letter or postcard that can be sent through the post or handed directly to the recipient</t>
+          <t>Electronic mode of delivery that involves presentation of information by an electronic device that is worn or carried on the body.</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes a watch, clip-on device, spectacles, in-ear devfice, vibrating device.</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr"/>
@@ -2036,7 +2075,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BCIO:011008</t>
+          <t>BCIO:011021</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2049,33 +2088,28 @@
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
-          <t>printed publication mode of delivery</t>
+          <t>call mode of delivery</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves use of of a printed publication.</t>
+          <t>Electronic mode of delivery that involves a communication process in which a signal is sent by a caller to a recipient to alert them of the communication intent, giving the recipient the opportunity to enage with the communication.</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Includes leaflets, brochures, newspapers, newsletter, booklets, magazines, manuals or worksheets.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BCIO:011007</t>
+          <t>BCIO:011022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2086,21 +2120,26 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>public notice mode of delivery</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>audio call mode of delivery</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves display of a poster, sign or notice in a public location.</t>
+          <t>Call mode of delivery that involves only audio information in the communication.</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes automated calls and audio messaging.</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr"/>
@@ -2109,7 +2148,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BCIO:011009</t>
+          <t>BCIO:011023</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2120,30 +2159,30 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>labelling mode of delivery</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>video call mode of delivery</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Printed material mode of delivery that involves information printed on a product or its packaging, or a label attached to or included with, a product or its packaging, and aims to convey information about that product.</t>
+          <t>Call mode of delivery that involves video and audio information in the communication.</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BCIO:011032</t>
+          <t>BCIO:011024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2153,22 +2192,27 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>textual mode of delivery</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>messaging mode of delivery</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves written text.</t>
+          <t>Call mode of delivery that involves textual information in the communication.</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Text message can include emojis, and additional audio and pictorial material. Includes SMS, WhatsApp and other messaging services.</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr"/>
@@ -2177,7 +2221,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BCIO:011010</t>
+          <t>BCIO:011025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2187,31 +2231,31 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>electronic mode of delivery</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>email mode of delivery</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Informational mode of delivery that involves electronic technology in the presentation of information to an intervention recipient.</t>
+          <t>Electronic mode of delivery that involves communication by email.</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BCIO:011020</t>
+          <t>BCIO:011028</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2224,33 +2268,28 @@
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>radio broadcast mode of delivery</t>
+          <t>mobile application mode of delivery</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of audio information that is broadcast and received by a radio receiver.</t>
+          <t>Electronic mode of delivery that involves the intervention recipient interacting with a mobile application.</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Includes digital radio and audio that is streamed as a podcast.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q54" t="inlineStr"/>
       <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BCIO:011026</t>
+          <t>BCIO:011030</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2260,31 +2299,31 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>video game mode of delivery</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>audio informational mode of delivery</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient playing a computer game.</t>
+          <t>Informational mode of delivery that involves sound.</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q55" t="inlineStr"/>
       <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BCIO:011017</t>
+          <t>BCIO:011031</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2294,36 +2333,31 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>3-D projection mode of delivery</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>visual informational mode of delivery</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of a 3-D image.</t>
+          <t>Informational mode of delivery that involves visual images.</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Includes hologram but does not include virtual reality headsets.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q56" t="inlineStr"/>
       <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BCIO:011013</t>
+          <t>BCIO:011032</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -2333,31 +2367,31 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>computer mode of delivery</t>
-        </is>
-      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>textual mode of delivery</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by a desktop or laptop computer.</t>
+          <t>Informational mode of delivery that involves written text.</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr"/>
       <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BCIO:011016</t>
+          <t>BCIO:050556</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -2367,27 +2401,27 @@
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>electronic environmental object mode of delivery</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>mass media mode of delivery</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves an electronic device positioned in the environment of the intervention recipient that can gather information and respond to commands.</t>
+          <t>Informational mode of delivery of radio broadcast, television, online press and printed press to a mass audience.</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Includes robots, and 'internet of things'.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>This is a form of mass media.</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr"/>
@@ -2396,7 +2430,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BCIO:011018</t>
+          <t>BCIO:011002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -2406,31 +2440,31 @@
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>virtual reality mode of delivery</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>human interactional mode of delivery</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves use of virtual reality through a virtual reality headset and optionally body movement sensors.</t>
+          <t>Informational mode of delivery that involves a person as intervention source who interacts with an intervention recipient in real time.</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q59" t="inlineStr"/>
       <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BCIO:011028</t>
+          <t>BCIO:011003</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -2443,28 +2477,28 @@
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr">
         <is>
-          <t>mobile application mode of delivery</t>
+          <t>face to face mode of delivery</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient interacting with a mobile application.</t>
+          <t>Human interactional mode of delivery that involves an intervention source and recipient being together in the same location and communicating directly.</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q60" t="inlineStr"/>
       <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>BCIO:011029</t>
+          <t>BCIO:011004</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -2477,28 +2511,28 @@
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr">
         <is>
-          <t>e-book mode of delivery</t>
+          <t>at-a-distance mode of delivery</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient being given access to an e-book.</t>
+          <t>Human interactional mode of delivery that involves an intervention source and recipient being in different locations and communicating through a communication channel.</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q61" t="inlineStr"/>
       <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BCIO:011012</t>
+          <t>BCIO:011005</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -2508,22 +2542,27 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>mobile digital device mode of delivery</t>
-        </is>
-      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>printed material mode of delivery</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by a handheld mobile digital device that can store, retrieve and process data.</t>
+          <t>Informational mode of delivery that involves use of printed material.</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Can include paper, acetate, text, diagrams and photographic images.</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr"/>
@@ -2532,7 +2571,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BCIO:011025</t>
+          <t>BCIO:011007</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -2545,28 +2584,28 @@
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t>email mode of delivery</t>
+          <t>public notice mode of delivery</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves communication by email.</t>
+          <t>Printed material mode of delivery that involves display of a poster, sign or notice in a public location.</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q63" t="inlineStr"/>
       <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>BCIO:011014</t>
+          <t>BCIO:011006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -2579,28 +2618,28 @@
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr">
         <is>
-          <t>electronic billboard mode of delivery</t>
+          <t>letter mode of delivery</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by an electronic screen positioned in a public location.</t>
+          <t>Printed material mode of delivery that involves a letter or postcard that can be sent through the post or handed directly to the recipient</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q64" t="inlineStr"/>
       <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BCIO:011015</t>
+          <t>BCIO:011009</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -2613,33 +2652,28 @@
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t>wearable electronic device mode of delivery</t>
+          <t>labelling mode of delivery</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information by an electronic device that is worn or carried on the body.</t>
+          <t>Printed material mode of delivery that involves information printed on a product or its packaging, or a label attached to or included with, a product or its packaging, and aims to convey information about that product.</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Includes a watch, clip-on device, spectacles, in-ear devfice, vibrating device.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q65" t="inlineStr"/>
       <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BCIO:011019</t>
+          <t>BCIO:011008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -2652,24 +2686,24 @@
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr">
         <is>
-          <t>playable electronic storage mode of delivery</t>
+          <t>printed publication mode of delivery</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information stored on an object that is inserted into a playing device.</t>
+          <t>Printed material mode of delivery that involves use of of a printed publication.</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Includes cassettes, video tapes, DVDs, CDs.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes leaflets, brochures, newspapers, newsletter, booklets, magazines, manuals or worksheets.</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr"/>
@@ -2678,7 +2712,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BCIO:011011</t>
+          <t>BCIO:011057</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -2687,37 +2721,32 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>group-based mode of delivery</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>television mode of delivery</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves presentation of information that is broadcast and displayed by television.</t>
+          <t>Mode of delivery that involves three or more people in the location where the intervention is delivered.</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Includes internet and satellite television.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q67" t="inlineStr"/>
       <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BCIO:011021</t>
+          <t>BCIO:011065</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -2726,23 +2755,28 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>arts feature mode of delivery</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>call mode of delivery</t>
-        </is>
-      </c>
+      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves a communication process in which a signal is sent by a caller to a recipient to alert them of the communication intent, giving the recipient the opportunity to enage with the communication.</t>
+          <t>Mode of delivery that involves application of creativity on the part of the intervention recipient.</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes art therapy, music therapy, dance and acting.</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr"/>
@@ -2751,7 +2785,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BCIO:011024</t>
+          <t>BCIO:011054</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -2760,28 +2794,28 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>somatic alteration mode of delivery</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>messaging mode of delivery</t>
-        </is>
-      </c>
+      <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves textual information in the communication.</t>
+          <t>Mode of of delivery that involves modifying the structure of the body of the recipient of the intervention.</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Text message can include emojis, and additional audio and pictorial material. Includes SMS, WhatsApp and other messaging services.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes surgery.</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr"/>
@@ -2790,7 +2824,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BCIO:011022</t>
+          <t>BCIO:011063</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -2799,37 +2833,32 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>pull mode of delivery</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>audio call mode of delivery</t>
-        </is>
-      </c>
+      <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves only audio information in the communication.</t>
+          <t>Mode of delivery that requires some action on the part of the recipient.</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Includes automated calls and audio messaging.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q70" t="inlineStr"/>
       <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BCIO:011023</t>
+          <t>BCIO:011033</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -2838,23 +2867,28 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>environmental change mode of delivery</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>video call mode of delivery</t>
-        </is>
-      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Call mode of delivery that involves video and audio information in the communication.</t>
+          <t>Mode of delivery that involves changing the physical shape, size, structure or appearance of objects in the environment of the intervention recipient.</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>This does not include use of textual or pictorial information. It includes lighting, speed humps, use of music, shape and size of containers of consumables.</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr"/>
@@ -2863,7 +2897,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BCIO:050558</t>
+          <t>BCIO:011059</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -2872,32 +2906,32 @@
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>interactional mode of delivery</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>online press mode of delivery</t>
-        </is>
-      </c>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery of a newspaper or magazine.</t>
+          <t>Mode of delivery in which there is causal influence from the intervention source to the recipient and from the recipient to the source.</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q72" t="inlineStr"/>
       <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BCIO:011027</t>
+          <t>BCIO:011064</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -2906,23 +2940,28 @@
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>gamification mode of delivery</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>website mode of delivery</t>
-        </is>
-      </c>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Electronic mode of delivery that involves the intervention recipient interacting with a website.</t>
+          <t>Mode of delivery that involves application of typical elements of game playing  to other areas of activity, typically as an online marketing technique to encourage engagement with a product or service.</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mode of delivery</t>
+          <t>Includes point scoring, competition with others, and rules of play.</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr"/>
@@ -2931,7 +2970,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BCIO:011064</t>
+          <t>BCIO:011056</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -2942,7 +2981,7 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>gamification mode of delivery</t>
+          <t>pair-based mode of delivery</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -2950,27 +2989,22 @@
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves application of typical elements of game playing  to other areas of activity, typically as an online marketing technique to encourage engagement with a product or service.</t>
+          <t>Mode of delivery that involves two recipients in the location where the intervention is delivered who have an interpersonal relationship.</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Includes point scoring, competition with others, and rules of play.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BCIO:011062</t>
+          <t>BCIO:011060</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -2981,7 +3015,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>push mode of delivery</t>
+          <t>synchronous mode of delivery</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -2989,22 +3023,22 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Mode of delivery that is not dependent on actions on the part of the intervention recipient.</t>
+          <t>Mode of delivery that involves delivery and receipt of the intervention or its components occurring at the same time or very close in time.</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BCIO:011065</t>
+          <t>BCIO:011062</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -3015,7 +3049,7 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>arts feature mode of delivery</t>
+          <t>push mode of delivery</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -3023,20 +3057,15 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves application of creativity on the part of the intervention recipient.</t>
+          <t>Mode of delivery that is not dependent on actions on the part of the intervention recipient.</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Includes art therapy, music therapy, dance and acting.</t>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
     </row>
@@ -3065,92 +3094,71 @@
           <t>Mode of delivery that involves one recipient in the location where the intervention is delivered.</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
+        </is>
+      </c>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BCIO:011033</t>
+          <t>COB:0000082</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>planned process</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>environmental change mode of delivery</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves changing the physical shape, size, structure or appearance of objects in the environment of the intervention recipient.</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>This does not include use of textual or pictorial information. It includes lighting, speed humps, use of music, shape and size of containers of consumables.</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
+          <t>A process that is initiated by an agent who intends to carry out a plan to achieve an objective through one or more actions as described in a plan specification.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>BCIO:011059</t>
+          <t>BCIO:037000</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
       <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>interactional mode of delivery</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Mode of delivery in which there is causal influence from the intervention source to the recipient and from the recipient to the source.</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
+          <t>A planned process that has the aim of influencing an outcome.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BCIO:011058</t>
+          <t>BCIO:003000</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -3158,33 +3166,25 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>uni-directional mode of delivery</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>behaviour change intervention</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Mode of delivery in which the only causal influence is from the intervention source to the recipient.</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
+          <t>An intervention that has the aim of influencing human behaviour.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BCIO:011057</t>
+          <t>BCIO:050557</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
@@ -3195,7 +3195,7 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>group-based mode of delivery</t>
+          <t>social influence intervention through mass media</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -3203,15 +3203,15 @@
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Mode of delivery that involves three or more people in the location where the intervention is delivered.</t>
+          <t>A behaviour change intervention that is an awareness of other people’s thoughts, feelings and actions BCT delivered through a mass media mode of delivery.</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Mode of delivery</t>
         </is>
       </c>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Mode of delivery</t>
-        </is>
-      </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
     </row>
